--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_individual_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_individual_h_6.xlsx
@@ -658,7 +658,7 @@
         <v>0.008454177761639635</v>
       </c>
       <c r="C2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>27457743</v>
+        <v>4262469</v>
       </c>
       <c r="L2" t="n">
-        <v>16048295</v>
+        <v>2175823</v>
       </c>
       <c r="M2" t="n">
-        <v>4018610</v>
+        <v>493005</v>
       </c>
       <c r="N2" t="n">
-        <v>206778</v>
+        <v>13943</v>
       </c>
       <c r="O2" t="n">
-        <v>2372040</v>
+        <v>291139</v>
       </c>
       <c r="P2" t="n">
-        <v>932284</v>
+        <v>113693</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999948740005493</v>
+        <v>0.999983549118042</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9049214720726013</v>
+        <v>0.8214280605316162</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8039684295654297</v>
+        <v>0.6683810949325562</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7593452334403992</v>
+        <v>0.5753355026245117</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4287776052951813</v>
+        <v>0.1302962303161621</v>
       </c>
       <c r="V2" t="n">
-        <v>0.802825927734375</v>
+        <v>0.633409321308136</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8742028474807739</v>
+        <v>0.7655526995658875</v>
       </c>
       <c r="X2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>28872412</v>
+        <v>4796855</v>
       </c>
       <c r="AG2" t="n">
-        <v>17836630</v>
+        <v>2983951</v>
       </c>
       <c r="AH2" t="n">
-        <v>4798928</v>
+        <v>801380</v>
       </c>
       <c r="AI2" t="n">
-        <v>353991</v>
+        <v>59049</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2755108</v>
+        <v>459641</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564692974090576</v>
+        <v>0.9560109972953796</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113166332244873</v>
+        <v>0.9115679264068604</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581637144088745</v>
+        <v>0.8585426211357117</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622001528739929</v>
+        <v>0.6615541577339172</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020119309425354</v>
+        <v>0.9020492434501648</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314349889755249</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002027047184025982</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>27457743</v>
+        <v>4262469</v>
       </c>
       <c r="E3" t="n">
-        <v>2644192</v>
+        <v>727626</v>
       </c>
       <c r="F3" t="n">
-        <v>43496</v>
+        <v>17262</v>
       </c>
       <c r="G3" t="n">
-        <v>4610</v>
+        <v>1341</v>
       </c>
       <c r="H3" t="n">
-        <v>1975</v>
+        <v>857</v>
       </c>
       <c r="I3" t="n">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="J3" t="n">
-        <v>60099537</v>
+        <v>10016518</v>
       </c>
       <c r="K3" t="n">
-        <v>64940514</v>
+        <v>10393365</v>
       </c>
       <c r="L3" t="n">
-        <v>74464111</v>
+        <v>11970802</v>
       </c>
       <c r="M3" t="n">
-        <v>91107677</v>
+        <v>15030672</v>
       </c>
       <c r="N3" t="n">
-        <v>97167137</v>
+        <v>16147189</v>
       </c>
       <c r="O3" t="n">
-        <v>94339222</v>
+        <v>15651162</v>
       </c>
       <c r="P3" t="n">
-        <v>96683420</v>
+        <v>16101342</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9106397032737732</v>
+        <v>0.8508588075637817</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8187724351882935</v>
+        <v>0.663510799407959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7180796265602112</v>
+        <v>0.5272594690322876</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3865074217319489</v>
+        <v>0.1560597270727158</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7762406468391418</v>
+        <v>0.5709290504455566</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8036757707595825</v>
+        <v>0.5877429842948914</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>28872412</v>
+        <v>4796855</v>
       </c>
       <c r="Z3" t="n">
-        <v>1187392</v>
+        <v>197460</v>
       </c>
       <c r="AA3" t="n">
-        <v>51135</v>
+        <v>8429</v>
       </c>
       <c r="AB3" t="n">
-        <v>40793</v>
+        <v>6823</v>
       </c>
       <c r="AC3" t="n">
-        <v>236</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>60099732</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>66511414</v>
+        <v>11099274</v>
       </c>
       <c r="AG3" t="n">
-        <v>76641422</v>
+        <v>12760866</v>
       </c>
       <c r="AH3" t="n">
-        <v>91588110</v>
+        <v>15262528</v>
       </c>
       <c r="AI3" t="n">
-        <v>97262032</v>
+        <v>16210047</v>
       </c>
       <c r="AJ3" t="n">
-        <v>94622500</v>
+        <v>15769750</v>
       </c>
       <c r="AK3" t="n">
-        <v>96738050</v>
+        <v>16122905</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575573801994324</v>
+        <v>0.9575310349464417</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100120067596436</v>
+        <v>0.9099469780921936</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575135469436646</v>
+        <v>0.8570606708526611</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6616765260696411</v>
+        <v>0.660917341709137</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015980958938599</v>
+        <v>0.9013646841049194</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312928318977356</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03199143872576704</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>2723271</v>
+        <v>871545</v>
       </c>
       <c r="E4" t="n">
-        <v>16048295</v>
+        <v>2175823</v>
       </c>
       <c r="F4" t="n">
-        <v>745067</v>
+        <v>200920</v>
       </c>
       <c r="G4" t="n">
-        <v>28314</v>
+        <v>10568</v>
       </c>
       <c r="H4" t="n">
-        <v>51640</v>
+        <v>18876</v>
       </c>
       <c r="I4" t="n">
-        <v>3834</v>
+        <v>1514</v>
       </c>
       <c r="J4" t="n">
-        <v>195</v>
+        <v>104</v>
       </c>
       <c r="K4" t="n">
-        <v>2884938</v>
+        <v>926627</v>
       </c>
       <c r="L4" t="n">
-        <v>3913055</v>
+        <v>1079540</v>
       </c>
       <c r="M4" t="n">
-        <v>1273594</v>
+        <v>363895</v>
       </c>
       <c r="N4" t="n">
-        <v>275472</v>
+        <v>93067</v>
       </c>
       <c r="O4" t="n">
-        <v>582573</v>
+        <v>168499</v>
       </c>
       <c r="P4" t="n">
-        <v>134155</v>
+        <v>34818</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999974370002747</v>
+        <v>0.999991774559021</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9077715873718262</v>
+        <v>0.8358844518661499</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8113029003143311</v>
+        <v>0.665937066078186</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7381361126899719</v>
+        <v>0.5502493977546692</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4065467119216919</v>
+        <v>0.1420190036296844</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7893095016479492</v>
+        <v>0.6005485057830811</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8374570608139038</v>
+        <v>0.6649665832519531</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1226769</v>
+        <v>206052</v>
       </c>
       <c r="Z4" t="n">
-        <v>17836630</v>
+        <v>2983951</v>
       </c>
       <c r="AA4" t="n">
-        <v>496804</v>
+        <v>82537</v>
       </c>
       <c r="AB4" t="n">
-        <v>32965</v>
+        <v>5520</v>
       </c>
       <c r="AC4" t="n">
-        <v>6858</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1314038</v>
+        <v>220718</v>
       </c>
       <c r="AG4" t="n">
-        <v>1735744</v>
+        <v>289476</v>
       </c>
       <c r="AH4" t="n">
-        <v>793161</v>
+        <v>132039</v>
       </c>
       <c r="AI4" t="n">
-        <v>180577</v>
+        <v>30209</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299295</v>
+        <v>49911</v>
       </c>
       <c r="AK4" t="n">
-        <v>79525</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570130109786987</v>
+        <v>0.9567704200744629</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910663902759552</v>
+        <v>0.9107567667961121</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.85783851146698</v>
+        <v>0.8578009605407715</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619382500648499</v>
+        <v>0.6612355709075928</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018049240112305</v>
+        <v>0.9017068147659302</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313638806343079</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>102502</v>
+        <v>37889</v>
       </c>
       <c r="E5" t="n">
-        <v>1074282</v>
+        <v>296003</v>
       </c>
       <c r="F5" t="n">
-        <v>4018610</v>
+        <v>493005</v>
       </c>
       <c r="G5" t="n">
-        <v>98017</v>
+        <v>29500</v>
       </c>
       <c r="H5" t="n">
-        <v>282429</v>
+        <v>71466</v>
       </c>
       <c r="I5" t="n">
-        <v>20483</v>
+        <v>7167</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2694405</v>
+        <v>747139</v>
       </c>
       <c r="L5" t="n">
-        <v>3552139</v>
+        <v>1103435</v>
       </c>
       <c r="M5" t="n">
-        <v>1577719</v>
+        <v>442028</v>
       </c>
       <c r="N5" t="n">
-        <v>328213</v>
+        <v>75401</v>
       </c>
       <c r="O5" t="n">
-        <v>683765</v>
+        <v>218800</v>
       </c>
       <c r="P5" t="n">
-        <v>227741</v>
+        <v>79747</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999980330467224</v>
+        <v>0.999993622303009</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9430549144744873</v>
+        <v>0.8975011110305786</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9238071441650391</v>
+        <v>0.8663179278373718</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9708983302116394</v>
+        <v>0.9506465196609497</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9938385486602783</v>
+        <v>0.9896832704544067</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9870752096176147</v>
+        <v>0.9762824177742004</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9963063597679138</v>
+        <v>0.9929842352867126</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>48155</v>
+        <v>8093</v>
       </c>
       <c r="Z5" t="n">
-        <v>510890</v>
+        <v>85757</v>
       </c>
       <c r="AA5" t="n">
-        <v>4798928</v>
+        <v>801380</v>
       </c>
       <c r="AB5" t="n">
-        <v>59714</v>
+        <v>9985</v>
       </c>
       <c r="AC5" t="n">
-        <v>174844</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1279736</v>
+        <v>212753</v>
       </c>
       <c r="AG5" t="n">
-        <v>1763804</v>
+        <v>295307</v>
       </c>
       <c r="AH5" t="n">
-        <v>797401</v>
+        <v>133653</v>
       </c>
       <c r="AI5" t="n">
-        <v>181000</v>
+        <v>30295</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300697</v>
+        <v>50298</v>
       </c>
       <c r="AK5" t="n">
-        <v>79702</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735268950462341</v>
+        <v>0.9734548926353455</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642821550369263</v>
+        <v>0.9641887545585632</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837660789489746</v>
+        <v>0.9837294220924377</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963095784187317</v>
+        <v>0.9962948560714722</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938762187957764</v>
+        <v>0.9938633441925049</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998374879360199</v>
+        <v>0.9983736872673035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>57257</v>
+        <v>15816</v>
       </c>
       <c r="E6" t="n">
-        <v>115688</v>
+        <v>20513</v>
       </c>
       <c r="F6" t="n">
-        <v>104193</v>
+        <v>27908</v>
       </c>
       <c r="G6" t="n">
-        <v>206778</v>
+        <v>13943</v>
       </c>
       <c r="H6" t="n">
-        <v>46903</v>
+        <v>10122</v>
       </c>
       <c r="I6" t="n">
-        <v>4123</v>
+        <v>1028</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>38779</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>32116</v>
+        <v>5368</v>
       </c>
       <c r="AA6" t="n">
-        <v>65335</v>
+        <v>10940</v>
       </c>
       <c r="AB6" t="n">
-        <v>353991</v>
+        <v>59049</v>
       </c>
       <c r="AC6" t="n">
-        <v>41884</v>
+        <v>6989</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1720</v>
+        <v>1319</v>
       </c>
       <c r="E7" t="n">
-        <v>74658</v>
+        <v>33211</v>
       </c>
       <c r="F7" t="n">
-        <v>365943</v>
+        <v>111336</v>
       </c>
       <c r="G7" t="n">
-        <v>135819</v>
+        <v>47855</v>
       </c>
       <c r="H7" t="n">
-        <v>2372040</v>
+        <v>291139</v>
       </c>
       <c r="I7" t="n">
-        <v>105616</v>
+        <v>25073</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4860</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>177905</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45512</v>
+        <v>7615</v>
       </c>
       <c r="AC7" t="n">
-        <v>2755108</v>
+        <v>459641</v>
       </c>
       <c r="AD7" t="n">
-        <v>72253</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>188</v>
+        <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>4235</v>
+        <v>2187</v>
       </c>
       <c r="F8" t="n">
-        <v>14895</v>
+        <v>6469</v>
       </c>
       <c r="G8" t="n">
-        <v>8712</v>
+        <v>3803</v>
       </c>
       <c r="H8" t="n">
-        <v>199626</v>
+        <v>67178</v>
       </c>
       <c r="I8" t="n">
-        <v>932284</v>
+        <v>113693</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1982</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1593</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75473</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
